--- a/code/data/combined/cmb+pelg-lcdm-free.xlsx
+++ b/code/data/combined/cmb+pelg-lcdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38828223.96926871</v>
+        <v>46603434.57894769</v>
       </c>
       <c r="C2" t="n">
-        <v>-133606560.1807298</v>
+        <v>-156395895.4990479</v>
       </c>
       <c r="D2" t="n">
-        <v>40456438.32679371</v>
+        <v>49287421.42409091</v>
       </c>
       <c r="E2" t="n">
-        <v>-530213.2286230297</v>
+        <v>-599801.1139433656</v>
       </c>
       <c r="F2" t="n">
-        <v>-1346163.240499784</v>
+        <v>-1366685.264801219</v>
       </c>
       <c r="G2" t="n">
-        <v>898216.1463236213</v>
+        <v>1147559.975288431</v>
       </c>
       <c r="H2" t="n">
-        <v>-2574861.584929749</v>
+        <v>-3111831.212573767</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-133606560.1807727</v>
+        <v>-156395895.4989889</v>
       </c>
       <c r="C3" t="n">
-        <v>885673649.1788267</v>
+        <v>948039414.2132279</v>
       </c>
       <c r="D3" t="n">
-        <v>-88909611.7808515</v>
+        <v>-116772303.812204</v>
       </c>
       <c r="E3" t="n">
-        <v>16001954.04965252</v>
+        <v>17157778.08243685</v>
       </c>
       <c r="F3" t="n">
-        <v>6683521.901879746</v>
+        <v>6767684.838575545</v>
       </c>
       <c r="G3" t="n">
-        <v>-3868534.01312273</v>
+        <v>-4746945.120741396</v>
       </c>
       <c r="H3" t="n">
-        <v>7937156.826177734</v>
+        <v>9501550.805630494</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40456438.32678897</v>
+        <v>49287421.42409782</v>
       </c>
       <c r="C4" t="n">
-        <v>-88909611.78078969</v>
+        <v>-116772303.8122902</v>
       </c>
       <c r="D4" t="n">
-        <v>48791138.15768781</v>
+        <v>58429231.28480382</v>
       </c>
       <c r="E4" t="n">
-        <v>880435.7659127319</v>
+        <v>850199.512403799</v>
       </c>
       <c r="F4" t="n">
-        <v>-889123.3338723651</v>
+        <v>-926442.8852653188</v>
       </c>
       <c r="G4" t="n">
-        <v>975967.5486275404</v>
+        <v>1243880.768179228</v>
       </c>
       <c r="H4" t="n">
-        <v>-2832694.826892702</v>
+        <v>-3439555.660249802</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-530213.2286246374</v>
+        <v>-599801.1139413137</v>
       </c>
       <c r="C5" t="n">
-        <v>16001954.04965715</v>
+        <v>17157778.0824309</v>
       </c>
       <c r="D5" t="n">
-        <v>880435.765910928</v>
+        <v>850199.5124060955</v>
       </c>
       <c r="E5" t="n">
-        <v>935381.25705797</v>
+        <v>1039507.572239652</v>
       </c>
       <c r="F5" t="n">
-        <v>44400.76214770368</v>
+        <v>59762.09668750666</v>
       </c>
       <c r="G5" t="n">
-        <v>-68216.51065416035</v>
+        <v>-77030.42810830986</v>
       </c>
       <c r="H5" t="n">
-        <v>-2808.1418270861</v>
+        <v>-2619.885118025416</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1346163.240499824</v>
+        <v>-1366685.264801558</v>
       </c>
       <c r="C6" t="n">
-        <v>6683521.901878514</v>
+        <v>6767684.838578036</v>
       </c>
       <c r="D6" t="n">
-        <v>-889123.3338725368</v>
+        <v>-926442.8852655226</v>
       </c>
       <c r="E6" t="n">
-        <v>44400.76214765399</v>
+        <v>59762.09668755529</v>
       </c>
       <c r="F6" t="n">
-        <v>581419.2640432602</v>
+        <v>593175.709124202</v>
       </c>
       <c r="G6" t="n">
-        <v>101143.0818919946</v>
+        <v>100542.1285781851</v>
       </c>
       <c r="H6" t="n">
-        <v>41673.44401517013</v>
+        <v>41864.24748417725</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>898216.1463237697</v>
+        <v>1147559.975288202</v>
       </c>
       <c r="C7" t="n">
-        <v>-3868534.013122165</v>
+        <v>-4746945.120742226</v>
       </c>
       <c r="D7" t="n">
-        <v>975967.5486278181</v>
+        <v>1243880.768178791</v>
       </c>
       <c r="E7" t="n">
-        <v>-68216.51065412255</v>
+        <v>-77030.4281083617</v>
       </c>
       <c r="F7" t="n">
-        <v>101143.0818919908</v>
+        <v>100542.1285781975</v>
       </c>
       <c r="G7" t="n">
-        <v>65777.78316533557</v>
+        <v>74404.77758571049</v>
       </c>
       <c r="H7" t="n">
-        <v>-71510.95842284086</v>
+        <v>-88431.20044808547</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2574861.584929677</v>
+        <v>-3111831.212573866</v>
       </c>
       <c r="C8" t="n">
-        <v>7937156.82617461</v>
+        <v>9501550.805634797</v>
       </c>
       <c r="D8" t="n">
-        <v>-2832694.826892942</v>
+        <v>-3439555.660249442</v>
       </c>
       <c r="E8" t="n">
-        <v>-2808.141827195487</v>
+        <v>-2619.885117885149</v>
       </c>
       <c r="F8" t="n">
-        <v>41673.44401516569</v>
+        <v>41864.24748415706</v>
       </c>
       <c r="G8" t="n">
-        <v>-71510.95842282892</v>
+        <v>-88431.20044810383</v>
       </c>
       <c r="H8" t="n">
-        <v>178347.6486300206</v>
+        <v>215664.7806681206</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+pelg-lcdm-free.xlsx
+++ b/code/data/combined/cmb+pelg-lcdm-free.xlsx
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46603434.57894769</v>
+        <v>43189604.82551879</v>
       </c>
       <c r="C2" t="n">
-        <v>-156395895.4990479</v>
+        <v>-145165973.5570866</v>
       </c>
       <c r="D2" t="n">
-        <v>49287421.42409091</v>
+        <v>45581849.69901282</v>
       </c>
       <c r="E2" t="n">
-        <v>-599801.1139433656</v>
+        <v>-580802.6110824668</v>
       </c>
       <c r="F2" t="n">
-        <v>-1366685.264801219</v>
+        <v>-1341304.424068137</v>
       </c>
       <c r="G2" t="n">
-        <v>1147559.975288431</v>
+        <v>1039709.188102167</v>
       </c>
       <c r="H2" t="n">
-        <v>-3111831.212573767</v>
+        <v>-2870677.146936723</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-156395895.4989889</v>
+        <v>-145165973.5570491</v>
       </c>
       <c r="C3" t="n">
-        <v>948039414.2132279</v>
+        <v>874616429.1965377</v>
       </c>
       <c r="D3" t="n">
-        <v>-116772303.812204</v>
+        <v>-109515064.849379</v>
       </c>
       <c r="E3" t="n">
-        <v>17157778.08243685</v>
+        <v>16373573.11385257</v>
       </c>
       <c r="F3" t="n">
-        <v>6767684.838575545</v>
+        <v>6564220.771037281</v>
       </c>
       <c r="G3" t="n">
-        <v>-4746945.120741396</v>
+        <v>-4379134.620822692</v>
       </c>
       <c r="H3" t="n">
-        <v>9501550.805630494</v>
+        <v>8787523.958876675</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49287421.42409782</v>
+        <v>45581849.69901667</v>
       </c>
       <c r="C4" t="n">
-        <v>-116772303.8122902</v>
+        <v>-109515064.8494324</v>
       </c>
       <c r="D4" t="n">
-        <v>58429231.28480382</v>
+        <v>53733421.12930765</v>
       </c>
       <c r="E4" t="n">
-        <v>850199.512403799</v>
+        <v>774714.2569319371</v>
       </c>
       <c r="F4" t="n">
-        <v>-926442.8852653188</v>
+        <v>-909309.7922938317</v>
       </c>
       <c r="G4" t="n">
-        <v>1243880.768179228</v>
+        <v>1128797.33038522</v>
       </c>
       <c r="H4" t="n">
-        <v>-3439555.660249802</v>
+        <v>-3167222.697126071</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-599801.1139413137</v>
+        <v>-580802.6110808</v>
       </c>
       <c r="C5" t="n">
-        <v>17157778.0824309</v>
+        <v>16373573.11384782</v>
       </c>
       <c r="D5" t="n">
-        <v>850199.5124060955</v>
+        <v>774714.2569338274</v>
       </c>
       <c r="E5" t="n">
-        <v>1039507.572239652</v>
+        <v>1014723.833225366</v>
       </c>
       <c r="F5" t="n">
-        <v>59762.09668750666</v>
+        <v>63199.67089658922</v>
       </c>
       <c r="G5" t="n">
-        <v>-77030.42810830986</v>
+        <v>-75223.71852179831</v>
       </c>
       <c r="H5" t="n">
-        <v>-2619.885118025416</v>
+        <v>-1917.5070347459</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1366685.264801558</v>
+        <v>-1341304.424068101</v>
       </c>
       <c r="C6" t="n">
-        <v>6767684.838578036</v>
+        <v>6564220.771037437</v>
       </c>
       <c r="D6" t="n">
-        <v>-926442.8852655226</v>
+        <v>-909309.792293765</v>
       </c>
       <c r="E6" t="n">
-        <v>59762.09668755529</v>
+        <v>63199.67089659788</v>
       </c>
       <c r="F6" t="n">
-        <v>593175.709124202</v>
+        <v>578240.9376349216</v>
       </c>
       <c r="G6" t="n">
-        <v>100542.1285781851</v>
+        <v>99794.77834159358</v>
       </c>
       <c r="H6" t="n">
-        <v>41864.24748417725</v>
+        <v>40391.60607225677</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1147559.975288202</v>
+        <v>1039709.188102006</v>
       </c>
       <c r="C7" t="n">
-        <v>-4746945.120742226</v>
+        <v>-4379134.620823367</v>
       </c>
       <c r="D7" t="n">
-        <v>1243880.768178791</v>
+        <v>1128797.330384919</v>
       </c>
       <c r="E7" t="n">
-        <v>-77030.4281083617</v>
+        <v>-75223.71852184847</v>
       </c>
       <c r="F7" t="n">
-        <v>100542.1285781975</v>
+        <v>99794.77834159348</v>
       </c>
       <c r="G7" t="n">
-        <v>74404.77758571049</v>
+        <v>70770.48036694758</v>
       </c>
       <c r="H7" t="n">
-        <v>-88431.20044808547</v>
+        <v>-80840.12957186837</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3111831.212573866</v>
+        <v>-2870677.14693679</v>
       </c>
       <c r="C8" t="n">
-        <v>9501550.805634797</v>
+        <v>8787523.958879497</v>
       </c>
       <c r="D8" t="n">
-        <v>-3439555.660249442</v>
+        <v>-3167222.697125876</v>
       </c>
       <c r="E8" t="n">
-        <v>-2619.885117885149</v>
+        <v>-1917.507034629101</v>
       </c>
       <c r="F8" t="n">
-        <v>41864.24748415706</v>
+        <v>40391.6060722604</v>
       </c>
       <c r="G8" t="n">
-        <v>-88431.20044810383</v>
+        <v>-80840.1295718817</v>
       </c>
       <c r="H8" t="n">
-        <v>215664.7806681206</v>
+        <v>198405.206502095</v>
       </c>
     </row>
   </sheetData>
